--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484179_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484179_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.8665</v>
+        <v>7.8685</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7412</v>
+        <v>6.0699</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1253</v>
+        <v>1.7986</v>
       </c>
       <c r="G2" t="n">
         <v>4.3572</v>
@@ -610,13 +610,13 @@
         <v>2.7774</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9454</v>
+        <v>0.0567</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5667</v>
+        <v>-0.238</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3787</v>
+        <v>0.2946</v>
       </c>
       <c r="V2" t="n">
         <v>0.6773</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>U. LATORRE CIRIA</t>
+          <t>B. ZICOVICH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7972</v>
+        <v>2.3637</v>
       </c>
       <c r="E3" t="n">
-        <v>6.2822</v>
+        <v>3.9477</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.485</v>
+        <v>-1.584</v>
       </c>
       <c r="G3" t="n">
-        <v>3.3342</v>
+        <v>0.5471</v>
       </c>
       <c r="H3" t="n">
-        <v>4.4755</v>
+        <v>1.3956</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.1412</v>
+        <v>-0.8485</v>
       </c>
       <c r="J3" t="n">
-        <v>6.2951</v>
+        <v>3.2457</v>
       </c>
       <c r="K3" t="n">
-        <v>6.1344</v>
+        <v>2.5202</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1606</v>
+        <v>0.7255</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.9608</v>
+        <v>-2.6985</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.659</v>
+        <v>-1.1246</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.3019</v>
+        <v>-1.574</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.5871</v>
+        <v>2.3806</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.9758</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3887</v>
+        <v>2.3806</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4367</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2245</v>
+        <v>-0.5044</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2122</v>
+        <v>-0.0596</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3866</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.7384</v>
+        <v>1.2065</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.125</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. ZICOVICH</t>
+          <t>U. LATORRE CIRIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7023</v>
+        <v>1.9769</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4546</v>
+        <v>4.9388</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.7523</v>
+        <v>-2.9619</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5471</v>
+        <v>3.3342</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3956</v>
+        <v>4.4755</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8485</v>
+        <v>-1.1412</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2457</v>
+        <v>6.2951</v>
       </c>
       <c r="K4" t="n">
-        <v>2.5202</v>
+        <v>6.1344</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7255</v>
+        <v>0.1606</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.6985</v>
+        <v>-2.9608</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1246</v>
+        <v>-1.659</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.574</v>
+        <v>-1.3019</v>
       </c>
       <c r="P4" t="n">
-        <v>2.3806</v>
+        <v>-1.5871</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.9758</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3806</v>
+        <v>1.3887</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.2255</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-0.1189</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2279</v>
+        <v>0.7353</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.3866</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2065</v>
+        <v>1.7384</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2065</v>
+        <v>-2.125</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6377</v>
+        <v>1.5816</v>
       </c>
       <c r="E5" t="n">
         <v>1.2681</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3696</v>
+        <v>0.3134</v>
       </c>
       <c r="G5" t="n">
         <v>0.8326</v>
@@ -844,13 +844,13 @@
         <v>0.7935</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8808</v>
+        <v>0.8247</v>
       </c>
       <c r="T5" t="n">
         <v>0.1191</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7617</v>
+        <v>0.7056</v>
       </c>
       <c r="V5" t="n">
         <v>-0.8692</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4063</v>
+        <v>0.4482</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6159</v>
+        <v>-0.3495</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0222</v>
+        <v>0.7977</v>
       </c>
       <c r="G6" t="n">
         <v>0.9778</v>
@@ -922,13 +922,13 @@
         <v>1.7855</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5248</v>
+        <v>0.5668</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1303</v>
+        <v>0.1361</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6551</v>
+        <v>0.4307</v>
       </c>
       <c r="V6" t="n">
         <v>1.0858</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. GER SIERRA</t>
+          <t>I. TERREROS RIVAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3858</v>
+        <v>-0.0561</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1094</v>
+        <v>-0.4625</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4952</v>
+        <v>0.4064</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7327</v>
+        <v>-0.2473</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0303</v>
+        <v>1.3812</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7631</v>
+        <v>-1.6285</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6705</v>
+        <v>1.5184</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6303</v>
+        <v>2.2337</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0402</v>
+        <v>-0.7153</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4032</v>
+        <v>-1.7658</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6</v>
+        <v>-0.8525</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8032</v>
+        <v>-0.9133</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.5952</v>
+        <v>0.3968</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3968</v>
+        <v>1.3887</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9419999999999999</v>
+        <v>-0.2055</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4308</v>
+        <v>-0.6518</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5112</v>
+        <v>0.4463</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.3373</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.3373</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. TERREROS RIVAS</t>
+          <t>R. GER SIERRA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5608</v>
+        <v>-0.6562</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9953</v>
+        <v>0.0073</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4345</v>
+        <v>-0.6635</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2473</v>
+        <v>-0.7327</v>
       </c>
       <c r="H8" t="n">
-        <v>1.3812</v>
+        <v>0.0303</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.6285</v>
+        <v>-0.7631</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5184</v>
+        <v>0.6705</v>
       </c>
       <c r="K8" t="n">
-        <v>2.2337</v>
+        <v>0.6303</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7153</v>
+        <v>0.0402</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.7658</v>
+        <v>-1.4032</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8525</v>
+        <v>-0.6</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9133</v>
+        <v>-0.8032</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3968</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3887</v>
+        <v>0.3968</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7102000000000001</v>
+        <v>0.6717</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.1846</v>
+        <v>0.3288</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4743</v>
+        <v>0.3429</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.3373</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3373</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0452</v>
+        <v>-1.1591</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0063</v>
+        <v>-1.6152</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9611</v>
+        <v>0.4561</v>
       </c>
       <c r="G9" t="n">
         <v>-3.8202</v>
@@ -1156,13 +1156,13 @@
         <v>2.7774</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2924</v>
+        <v>0.1785</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6291</v>
+        <v>-0.238</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9214</v>
+        <v>0.4164</v>
       </c>
       <c r="V9" t="n">
         <v>1.689</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.871</v>
+        <v>-1.4807</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6928</v>
+        <v>-0.3867</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1782</v>
+        <v>-1.094</v>
       </c>
       <c r="G10" t="n">
         <v>-0.381</v>
@@ -1234,13 +1234,13 @@
         <v>1.3887</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4144</v>
+        <v>-0.0241</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3741</v>
+        <v>-0.068</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0403</v>
+        <v>0.0439</v>
       </c>
       <c r="V10" t="n">
         <v>-1.4724</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.2151</v>
+        <v>-4.6197</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5861</v>
+        <v>-2.5237</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.6291</v>
+        <v>-2.096</v>
       </c>
       <c r="G11" t="n">
         <v>-2.7868</v>
@@ -1312,13 +1312,13 @@
         <v>0.7935</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9029</v>
+        <v>-0.3075</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.442</v>
+        <v>-0.3797</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4609</v>
+        <v>0.0722</v>
       </c>
       <c r="V11" t="n">
         <v>-1.3271</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.332100000000001</v>
+        <v>6.267100000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>9.959099999999999</v>
+        <v>10.8942</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.6271</v>
+        <v>-4.6272</v>
       </c>
       <c r="G12" t="n">
-        <v>2.080899999999999</v>
+        <v>2.080900000000001</v>
       </c>
       <c r="H12" t="n">
         <v>10.0808</v>
@@ -1381,7 +1381,7 @@
         <v>-7.1247</v>
       </c>
       <c r="P12" t="n">
-        <v>2.975699999999999</v>
+        <v>2.9757</v>
       </c>
       <c r="Q12" t="n">
         <v>-12.8949</v>
@@ -1390,13 +1390,13 @@
         <v>15.8708</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8782999999999996</v>
+        <v>1.8137</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.5499</v>
+        <v>-1.6148</v>
       </c>
       <c r="U12" t="n">
-        <v>3.4281</v>
+        <v>3.4283</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6032</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. TARRIDA TORRES</t>
+          <t>I. DRIOUECH ELMRABET</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.5633</v>
+        <v>1.2418</v>
       </c>
       <c r="E13" t="n">
-        <v>3.5368</v>
+        <v>1.1827</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.9735</v>
+        <v>0.0591</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.4546</v>
+        <v>1.1794</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0197</v>
+        <v>-0.2016</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.4744</v>
+        <v>1.381</v>
       </c>
       <c r="J13" t="n">
-        <v>2.1322</v>
+        <v>1.245</v>
       </c>
       <c r="K13" t="n">
-        <v>2.6868</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.5546</v>
+        <v>1.245</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.5868</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.667</v>
+        <v>-0.2016</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.9198</v>
+        <v>0.136</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9919</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1903</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1822</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.76</v>
+        <v>0.0623</v>
       </c>
       <c r="T13" t="n">
-        <v>1.797</v>
+        <v>-0.0623</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0369</v>
+        <v>0.1247</v>
       </c>
       <c r="V13" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.7979000000000001</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.532</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I. DRIOUECH ELMRABET</t>
+          <t>N. BAQUES GARCIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.354</v>
+        <v>0.8133</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1827</v>
+        <v>1.3469</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1713</v>
+        <v>-0.5336</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1794</v>
+        <v>0.5079</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.2016</v>
+        <v>-1.4264</v>
       </c>
       <c r="I14" t="n">
-        <v>1.381</v>
+        <v>1.9343</v>
       </c>
       <c r="J14" t="n">
-        <v>1.245</v>
+        <v>4.2849</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1.7095</v>
       </c>
       <c r="L14" t="n">
-        <v>1.245</v>
+        <v>2.5754</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-3.777</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2016</v>
+        <v>-3.1359</v>
       </c>
       <c r="O14" t="n">
-        <v>0.136</v>
+        <v>-0.6412</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-2.7774</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-5.158</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.3806</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1746</v>
+        <v>0.4039</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0623</v>
+        <v>-0.459</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2369</v>
+        <v>0.8628</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>2.6789</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.6789</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>N. BAQUES GARCIA</t>
+          <t>A. TARRIDA TORRES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4893</v>
+        <v>0.3772</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9388</v>
+        <v>2.2104</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4494</v>
+        <v>-1.8332</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5079</v>
+        <v>-1.4546</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.4264</v>
+        <v>0.0197</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9343</v>
+        <v>-1.4744</v>
       </c>
       <c r="J15" t="n">
-        <v>4.2849</v>
+        <v>2.1322</v>
       </c>
       <c r="K15" t="n">
-        <v>1.7095</v>
+        <v>2.6868</v>
       </c>
       <c r="L15" t="n">
-        <v>2.5754</v>
+        <v>-0.5546</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.777</v>
+        <v>-3.5868</v>
       </c>
       <c r="N15" t="n">
-        <v>-3.1359</v>
+        <v>-2.667</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6412</v>
+        <v>-0.9198</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.7774</v>
+        <v>0.9919</v>
       </c>
       <c r="Q15" t="n">
-        <v>-5.158</v>
+        <v>-1.1903</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3806</v>
+        <v>2.1822</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0799</v>
+        <v>0.5739</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8671</v>
+        <v>0.4706</v>
       </c>
       <c r="U15" t="n">
-        <v>0.947</v>
+        <v>0.1034</v>
       </c>
       <c r="V15" t="n">
-        <v>2.6789</v>
+        <v>0.266</v>
       </c>
       <c r="W15" t="n">
-        <v>2.6789</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4642</v>
+        <v>0.3468</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4062</v>
+        <v>-0.1039</v>
       </c>
       <c r="F16" t="n">
-        <v>0.058</v>
+        <v>0.4508</v>
       </c>
       <c r="G16" t="n">
         <v>0.0484</v>
@@ -1702,13 +1702,13 @@
         <v>1.7855</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1543</v>
+        <v>0.0369</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3742</v>
+        <v>-0.1359</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.22</v>
+        <v>0.1728</v>
       </c>
       <c r="V16" t="n">
         <v>-0.532</v>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0203</v>
+        <v>0.1837</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1549</v>
+        <v>0.3589</v>
       </c>
       <c r="F17" t="n">
         <v>-0.1752</v>
@@ -1780,10 +1780,10 @@
         <v>0.7935</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.128</v>
+        <v>-0.9239000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-0.7935</v>
       </c>
       <c r="U17" t="n">
         <v>-0.1304</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4011</v>
+        <v>-0.0338</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3271</v>
+        <v>0.4891</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.074</v>
+        <v>-0.5229</v>
       </c>
       <c r="G18" t="n">
         <v>0.2926</v>
@@ -1858,13 +1858,13 @@
         <v>2.1822</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.305</v>
+        <v>0.0623</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.4226</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>1.1176</v>
+        <v>0.6687</v>
       </c>
       <c r="V18" t="n">
         <v>0.6032</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. RIBAS BLANCO</t>
+          <t>A. ALEXANDRE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5165</v>
+        <v>-0.3525</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.002</v>
+        <v>1.5615</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5145</v>
+        <v>-1.914</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2069</v>
+        <v>-1.2202</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3831</v>
+        <v>-1.6323</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1762</v>
+        <v>0.4121</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0603</v>
+        <v>2.301</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0202</v>
+        <v>1.3773</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0402</v>
+        <v>0.9237</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2672</v>
+        <v>-3.5212</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4032</v>
+        <v>-3.0096</v>
       </c>
       <c r="O19" t="n">
-        <v>0.136</v>
+        <v>-0.5117</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.1903</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.1984</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.3887</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0436</v>
+        <v>0.2806</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0623</v>
+        <v>-0.2039</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0187</v>
+        <v>0.4845</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.266</v>
+        <v>-0.6032</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.3373</v>
       </c>
       <c r="X19" t="n">
         <v>-0.266</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. ALEXANDRE</t>
+          <t>R. RIBAS BLANCO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6229</v>
+        <v>-0.3864</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4594</v>
+        <v>0.1</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.0823</v>
+        <v>-0.4864</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.2202</v>
+        <v>-0.2069</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.6323</v>
+        <v>-0.3831</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4121</v>
+        <v>0.1762</v>
       </c>
       <c r="J20" t="n">
-        <v>2.301</v>
+        <v>0.0603</v>
       </c>
       <c r="K20" t="n">
-        <v>1.3773</v>
+        <v>0.0202</v>
       </c>
       <c r="L20" t="n">
-        <v>0.9237</v>
+        <v>0.0402</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.5212</v>
+        <v>-0.2672</v>
       </c>
       <c r="N20" t="n">
-        <v>-3.0096</v>
+        <v>-0.4032</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5117</v>
+        <v>0.136</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1903</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.1984</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3887</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0102</v>
+        <v>0.0864</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.306</v>
+        <v>0.0397</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3162</v>
+        <v>0.0468</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6032</v>
+        <v>-0.266</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3373</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>-0.266</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8668</v>
+        <v>-1.7954</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0567</v>
+        <v>0.3514</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8101</v>
+        <v>-2.1468</v>
       </c>
       <c r="G21" t="n">
         <v>0.8735000000000001</v>
@@ -2092,13 +2092,13 @@
         <v>0.7935</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3435</v>
+        <v>-0.2721</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1222</v>
+        <v>-0.7141</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7786999999999999</v>
+        <v>0.442</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2065</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3236</v>
+        <v>-2.5455</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8916</v>
+        <v>-2.1977</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4321</v>
+        <v>-0.3479</v>
       </c>
       <c r="G22" t="n">
         <v>-0.5485</v>
@@ -2170,13 +2170,13 @@
         <v>0.3968</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2556</v>
+        <v>-0.4775</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0056</v>
+        <v>-0.3117</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.25</v>
+        <v>-0.1658</v>
       </c>
       <c r="V22" t="n">
         <v>0.266</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4515</v>
+        <v>-3.1812</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7741</v>
+        <v>-0.6721</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.6774</v>
+        <v>-2.5091</v>
       </c>
       <c r="G23" t="n">
         <v>-2.2039</v>
@@ -2248,13 +2248,13 @@
         <v>0.9919</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9817</v>
+        <v>-0.7113</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7537</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2279</v>
+        <v>-0.0596</v>
       </c>
       <c r="V23" t="n">
         <v>-0.266</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.331899999999999</v>
+        <v>-5.332000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>4.627300000000001</v>
+        <v>4.6272</v>
       </c>
       <c r="F24" t="n">
-        <v>-9.959200000000001</v>
+        <v>-9.959199999999999</v>
       </c>
       <c r="G24" t="n">
         <v>-2.081</v>
@@ -2326,10 +2326,10 @@
         <v>12.8949</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8783999999999998</v>
+        <v>-0.8785000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.4281</v>
+        <v>-3.4282</v>
       </c>
       <c r="U24" t="n">
         <v>2.5499</v>
